--- a/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>As Device Profile</t>
+    <t>AS Device Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de la ressource Device dans le contexte de l'Annuaire Santé pour décrire les équipements matériels lourds ('EML') mis en oeuvre au sein d'un établissement.</t>
+    <t>Profil créé à partir de Device dans le contexte de l'Annuaire Santé pour décrire les équipements matériels lourds ('EML') mis en oeuvre au sein d'un établissement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -463,7 +463,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de l'identifiant métier de l'autorisation ARHGOS d’un équipement matériel lourd.</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
+    <t>Synonyme : numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>Device.extension:as-ext-device-authorization-date-device</t>
@@ -906,7 +906,7 @@
     <t>The serial number assigned by the organization when the device was manufactured.</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroSerie</t>
+    <t>Synonyme : numeroSerie</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].id</t>
@@ -995,7 +995,7 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>Synonyme MOS : equipementMaterielLourd</t>
+    <t>Synonyme : equipementMaterielLourd</t>
   </si>
   <si>
     <t>Liste des types d'EML</t>
@@ -1182,7 +1182,7 @@
     <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
-    <t>Synonyme MOS : idStructure</t>
+    <t>Synonyme : idStructure</t>
   </si>
   <si>
     <t>.playedRole[typeCode=OWN].scoper</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
